--- a/Datas/DefaultConfigData.xlsx
+++ b/Datas/DefaultConfigData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -46,6 +46,10 @@
   </si>
   <si>
     <t>Committer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>LogShow</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -382,7 +386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:B5"/>
+  <dimension ref="A2:B6"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.875" customWidth="1"/>
@@ -416,6 +420,14 @@
     <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/DefaultConfigData.xlsx
+++ b/Datas/DefaultConfigData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>string</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -50,6 +50,37 @@
   </si>
   <si>
     <t>LogShow</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AboutInfo</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DeveloperInfo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">制作人(Producer)：shanflyer（小红书(redNote):94980247969）
+策划(Designer)：shanflyer
+程序(Programmer)：shanflyer
+美术(Artist)：shanflyer、肚子会好饿（小红书(redNote):26263379626）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Partial Flower Baskets: captainskolot @https://captainskolot.itch.io/\n
+Partial Maps: winlu @https://winlu.itch.io/, verzatiledev @https://verzatiledev.itch.io/, aamatniekss @https://aamatniekss.itch.io/, kokororeflections @https://kokororeflections.itch.io/\n
+Animals: finalbossblues @https://finalbossblues.itch.io/\n
+Fish-related Icons: PixelOdussey @https://pixelodyssey.itch.io/\n
+Skill Icons:whisperltd @https://whisperltd.itch.io/\n
+Food Icons:PixelOdussey @https://pixelodyssey.itch.io/\n
+Miscellaneous Icons: PixelOdussey @https://pixelodyssey.itch.io/\n
+UI Resources:pavelreem @https://www.gamedevmarket.net/member/pavelreem\n
+Character Sprites: Tonbi @ Tobishima-Factory &amp; KADOKAWA CORPORATION\n
+Crops:bluecarrot16, Daniel Eddeland (daneeklu), Joshua Taylor, Richard Kettering (Jetrel). Commissioned by castelonia. License: CC-BY-SA 3.0+ or GPL 3.0+. https://opengameart.org/content/lpc-crops\n
+Sound Effects &amp; Music​: wowsound @https://wowsound.itch.io/, magicsoundeffect s@https://magicsoundeffects.itch.io/, ElvGames @https://elvgames.itch.io/, leohpaz @https://leohpaz.itch.io/\n\n
+If your work is missing from the credits, please contact me at shanflyer@qq.com.
+Thank you to everyone involved!</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -102,9 +133,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -386,7 +420,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:B6"/>
+  <dimension ref="A2:B8"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.875" customWidth="1"/>
@@ -430,6 +464,22 @@
         <v>0</v>
       </c>
     </row>
+    <row r="7" spans="1:2" ht="213.75" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="71.25" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>

--- a/Datas/DefaultConfigData.xlsx
+++ b/Datas/DefaultConfigData.xlsx
@@ -60,14 +60,6 @@
     <t>DeveloperInfo</t>
   </si>
   <si>
-    <t xml:space="preserve">制作人(Producer)：shanflyer（小红书(redNote):94980247969）
-策划(Designer)：shanflyer
-程序(Programmer)：shanflyer
-美术(Artist)：shanflyer、肚子会好饿（小红书(redNote):26263379626）
-</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Partial Flower Baskets: captainskolot @https://captainskolot.itch.io/\n
 Partial Maps: winlu @https://winlu.itch.io/, verzatiledev @https://verzatiledev.itch.io/, aamatniekss @https://aamatniekss.itch.io/, kokororeflections @https://kokororeflections.itch.io/\n
 Animals: finalbossblues @https://finalbossblues.itch.io/\n
@@ -75,12 +67,16 @@
 Skill Icons:whisperltd @https://whisperltd.itch.io/\n
 Food Icons:PixelOdussey @https://pixelodyssey.itch.io/\n
 Miscellaneous Icons: PixelOdussey @https://pixelodyssey.itch.io/\n
-UI Resources:pavelreem @https://www.gamedevmarket.net/member/pavelreem\n
-Character Sprites: Tonbi @ Tobishima-Factory &amp; KADOKAWA CORPORATION\n
+UI Resources:pavelreem @https://www.gamedevmarket.net/member/pavelreem\n 
 Crops:bluecarrot16, Daniel Eddeland (daneeklu), Joshua Taylor, Richard Kettering (Jetrel). Commissioned by castelonia. License: CC-BY-SA 3.0+ or GPL 3.0+. https://opengameart.org/content/lpc-crops\n
 Sound Effects &amp; Music​: wowsound @https://wowsound.itch.io/, magicsoundeffect s@https://magicsoundeffects.itch.io/, ElvGames @https://elvgames.itch.io/, leohpaz @https://leohpaz.itch.io/\n\n
 If your work is missing from the credits, please contact me at shanflyer@qq.com.
 Thank you to everyone involved!</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">制作人(Producer)：shanflyer（小红书(redNote):94980247969）\n策划(Designer)：shanflyer\n程序(Programmer)：shanflyer\n美术(Artist)：shanflyer、肚子会好饿（小红书(redNote):26263379626）
+</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -464,20 +460,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="213.75" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="199.5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="71.25" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/DefaultConfigData.xlsx
+++ b/Datas/DefaultConfigData.xlsx
@@ -60,22 +60,23 @@
     <t>DeveloperInfo</t>
   </si>
   <si>
-    <t>Partial Flower Baskets: captainskolot @https://captainskolot.itch.io/\n
-Partial Maps: winlu @https://winlu.itch.io/, verzatiledev @https://verzatiledev.itch.io/, aamatniekss @https://aamatniekss.itch.io/, kokororeflections @https://kokororeflections.itch.io/\n
-Animals: finalbossblues @https://finalbossblues.itch.io/\n
-Fish-related Icons: PixelOdussey @https://pixelodyssey.itch.io/\n
-Skill Icons:whisperltd @https://whisperltd.itch.io/\n
-Food Icons:PixelOdussey @https://pixelodyssey.itch.io/\n
-Miscellaneous Icons: PixelOdussey @https://pixelodyssey.itch.io/\n
-UI Resources:pavelreem @https://www.gamedevmarket.net/member/pavelreem\n 
-Crops:bluecarrot16, Daniel Eddeland (daneeklu), Joshua Taylor, Richard Kettering (Jetrel). Commissioned by castelonia. License: CC-BY-SA 3.0+ or GPL 3.0+. https://opengameart.org/content/lpc-crops\n
-Sound Effects &amp; Music​: wowsound @https://wowsound.itch.io/, magicsoundeffect s@https://magicsoundeffects.itch.io/, ElvGames @https://elvgames.itch.io/, leohpaz @https://leohpaz.itch.io/\n\n
-If your work is missing from the credits, please contact me at shanflyer@qq.com.
-Thank you to everyone involved!</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t xml:space="preserve">制作人(Producer)：shanflyer（小红书(redNote):94980247969）\n策划(Designer)：shanflyer\n程序(Programmer)：shanflyer\n美术(Artist)：shanflyer、肚子会好饿（小红书(redNote):26263379626）
+</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Partial Flower Baskets: &lt;link="https://captainskolot.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;captainskolot @https://captainskolot.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;\n
+Partial Maps: &lt;link="https://winlu.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;winlu @https://winlu.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;, &lt;link="https://verzatiledev.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;verzatiledev @https://verzatiledev.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;, &lt;link="https://aamatniekss.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;aamatniekss @https://aamatniekss.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;, &lt;link="https://kokororeflections.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;kokororeflections @https://kokororeflections.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;\n
+Animals: &lt;link="https://finalbossblues.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;finalbossblues @https://finalbossblues.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;\n
+Fish-related Icons: &lt;link="https://pixelodyssey.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;PixelOdyssey @https://pixelodyssey.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;\n
+Skill Icons: &lt;link="https://whisperltd.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;whisperltd @https://whisperltd.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;\n
+Food Icons: &lt;link="https://pixelodyssey.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;PixelOdyssey @https://pixelodyssey.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;\n
+Miscellaneous Icons: &lt;link="https://pixelodyssey.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;PixelOdyssey @https://pixelodyssey.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;\n
+UI Resources: &lt;link="https://www.gamedevmarket.net/member/pavelreem"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;pavelreem @https://www.gamedevmarket.net/member/pavelreem&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;\n
+Crops: bluecarrot16, Daniel Eddeland (daneeklu), Joshua Taylor, Richard Kettering (Jetrel). Commissioned by castelonia. License: CC-BY-SA 3.0+ or GPL 3.0+. &lt;link="https://opengameart.org/content/lpc-crops"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;https://opengameart.org/content/lpc-crops&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;\n
+Sound Effects &amp; Music: &lt;link="https://wowsound.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;wowsound @https://wowsound.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;, &lt;link="https://magicsoundeffects.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;magicsoundeffects @https://magicsoundeffects.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;, &lt;link="https://elvgames.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;ElvGames @https://elvgames.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;, &lt;link="https://leohpaz.itch.io/"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;leohpaz @https://leohpaz.itch.io/&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;\n\n
+If your work is missing from the credits, please contact me at &lt;link="mailto:shanflyer@qq.com"&gt;&lt;color=#3DA0FF&gt;&lt;u&gt;shanflyer@qq.com&lt;/u&gt;&lt;/color&gt;&lt;/link&gt;.\n
+Thank you to everyone involved!
 </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -460,12 +461,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="199.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:2" ht="270.75" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>8</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="42.75" x14ac:dyDescent="0.2">
@@ -473,7 +474,7 @@
         <v>9</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
